--- a/stories/arbres/ATOM-JEU.FOOT.001-06.xlsx
+++ b/stories/arbres/ATOM-JEU.FOOT.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Flore et papa sont au jardin. Papa pose deux sacs. C'est le but. Il trace un rectangle. Papa dit : voici l'espace montré. On reste dans l'espace montré. Flore touche le ballon. Papa dit : on va passer le ballon. Puis on vise le but. Flore passe. Papa rend. Flore pousse le ballon vers le but. Les pieds restent dans l'espace montré.</t>
+          <t>Flore et papa sont au jardin. Papa pose deux sacs. C'est le but. Il trace un rectangle. Voici l'espace montré. On reste dans l'espace montré. Flore touche le ballon. On va passer le ballon. Puis on vise le but. Flore passe. Papa rend. Flore pousse le ballon vers le but. Les pieds restent dans l'espace montré.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Flore et papa sont au jardin. Papa pose deux sacs. C'est le but. Il trace un rectangle.
+papa|Voici l'espace montré. On reste dans l'espace montré.
+narrateur|Flore touche le ballon.
+papa|On va passer le ballon.
+narrateur|Puis on vise le but. Flore passe. Papa rend. Flore pousse le ballon vers le but. Les pieds restent dans l'espace montré.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Flore joue au foot. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Flore a passé le ballon. Elle a visé le but. Dans l'espace montré.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa range les sacs. Flore boit une gorgée.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.FOOT.001-06.xlsx
+++ b/stories/arbres/ATOM-JEU.FOOT.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Puis on vise le but. Flore passe. Papa rend. Flore pousse le ballon vers le but. Les pieds restent dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Flore joue au foot. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Flore a passé le ballon. Elle a visé le but. Dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1839,7 @@
           <t>narrateur|Papa range les sacs. Flore boit une gorgée.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.FOOT.001-06.xlsx
+++ b/stories/arbres/ATOM-JEU.FOOT.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Flore vise le but au jardin</t>
+          <t>Les sacs de Mila au jardin</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Après la pluie, Mila et papa font un petit foot entre deux sacs. Elle passe, elle vise le but, les pieds dans l'espace montré.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Flore et papa sont au jardin. Papa pose deux sacs. C'est le but. Il trace un rectangle. Voici l'espace montré. On reste dans l'espace montré. Flore touche le ballon. On va passer le ballon. Puis on vise le but. Flore passe. Papa rend. Flore pousse le ballon vers le but. Les pieds restent dans l'espace montré.</t>
+          <t>Une goutte tombe de la gouttière. Elle fait ding dans le seau gris. Le romarin sent fort, tout près. Les sandales sèchent sur la dalle chaude. Une aile jaune passe au-dessus des pots. Tu as entendu le seau, Mila ? Oui, papa. Ça fait ding. En ce moment, le ballon attend dans l'herbe. L'herbe est encore un peu mouillée. Mila pose la paume sur le ballon. Il est souple, papa. Oui. Il est souple et lisse. Papa pose deux sacs au fond du jardin. C'est le but. Les sacs sont beiges et un peu râpeux. Papa trace un rectangle dans l'herbe. Voici l'espace montré. On reste dans l'espace montré. Dans le rectangle ? Oui. Les pieds restent ici. Mila avance dans l'espace montré. Ses chaussettes vertes sont un peu humides. On va passer le ballon. Puis on vise le but. Mila pousse le ballon vers papa. Le ballon roule, tout mou, dans l'herbe. Bien. Tu as passé le ballon. Papa le rend, tout doucement. Mila le reçoit dans l'espace montré. Maintenant, vise le but. Mila pousse le ballon vers les sacs. Le ballon glisse entre les deux sacs. Il est au fond ! Bravo. Tu as visé le but. Les pieds sont restés dans l'espace montré. Mila ramène le ballon contre son ventre. Une goutte tombe encore dans le seau. On recommence. On passe, puis le but. Mila passe encore le ballon. Papa rend encore le ballon. Mila vise encore le but. Le ballon touche un sac, puis entre. Bravo, Mila. Tu as fait du bon travail. On reste dans l'espace montré. Oui. On passe. On vise le but. Mila essuie une goutte sur le ballon. Le ballon sent l'herbe mouillée. Tu as fini ce tour ? Oui, papa. Bravo. On boit un peu d'eau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,58 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Flore et papa sont au jardin. Papa pose deux sacs. C'est le but. Il trace un rectangle.
-papa|Voici l'espace montré. On reste dans l'espace montré.
-narrateur|Flore touche le ballon.
+          <t>narrateur|Une goutte tombe de la gouttière.
+narrateur|Elle fait ding dans le seau gris.
+narrateur|Le romarin sent fort, tout près.
+narrateur|Les sandales sèchent sur la dalle chaude.
+narrateur|Une aile jaune passe au-dessus des pots.
+papa|Tu as entendu le seau, Mila ?
+enfant-f|Oui, papa. Ça fait ding.
+narrateur|En ce moment, le ballon attend dans l'herbe.
+narrateur|L'herbe est encore un peu mouillée.
+narrateur|Mila pose la paume sur le ballon.
+enfant-f|Il est souple, papa.
+papa|Oui. Il est souple et lisse.
+narrateur|Papa pose deux sacs au fond du jardin.
+papa|C'est le but.
+narrateur|Les sacs sont beiges et un peu râpeux.
+narrateur|Papa trace un rectangle dans l'herbe.
+papa|Voici l'espace montré.
+papa|On reste dans l'espace montré.
+enfant-f|Dans le rectangle ?
+papa|Oui. Les pieds restent ici.
+narrateur|Mila avance dans l'espace montré.
+narrateur|Ses chaussettes vertes sont un peu humides.
 papa|On va passer le ballon.
-narrateur|Puis on vise le but. Flore passe. Papa rend. Flore pousse le ballon vers le but. Les pieds restent dans l'espace montré.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|Puis on vise le but.
+narrateur|Mila pousse le ballon vers papa.
+narrateur|Le ballon roule, tout mou, dans l'herbe.
+papa|Bien. Tu as passé le ballon.
+narrateur|Papa le rend, tout doucement.
+narrateur|Mila le reçoit dans l'espace montré.
+papa|Maintenant, vise le but.
+narrateur|Mila pousse le ballon vers les sacs.
+narrateur|Le ballon glisse entre les deux sacs.
+enfant-f|Il est au fond !
+papa|Bravo. Tu as visé le but.
+papa|Les pieds sont restés dans l'espace montré.
+narrateur|Mila ramène le ballon contre son ventre.
+narrateur|Une goutte tombe encore dans le seau.
+papa|On recommence. On passe, puis le but.
+narrateur|Mila passe encore le ballon.
+narrateur|Papa rend encore le ballon.
+narrateur|Mila vise encore le but.
+narrateur|Le ballon touche un sac, puis entre.
+papa|Bravo, Mila. Tu as fait du bon travail.
+enfant-f|On reste dans l'espace montré.
+papa|Oui. On passe. On vise le but.
+narrateur|Mila essuie une goutte sur le ballon.
+narrateur|Le ballon sent l'herbe mouillée.
+papa|Tu as fini ce tour ?
+enfant-f|Oui, papa.
+papa|Bravo. On boit un peu d'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1400,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Flore joue au foot. Que fait-elle ?</t>
+          <t>Mila joue au foot. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,10 +1556,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Flore joue au foot. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Mila joue au foot.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1528,7 +1584,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Flore a passé le ballon. Elle a visé le but. Dans l'espace montré.</t>
+          <t>Mila a passé le ballon. Elle a visé le but. Les pieds sont restés dans l'espace montré. Tu as passé, puis visé le but ? Oui. Dans l'espace montré. Bravo. C'est du bon travail. Le seau fait encore un petit ding. L'aile jaune n'est plus là.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,10 +1728,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Flore a passé le ballon. Elle a visé le but. Dans l'espace montré.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Mila a passé le ballon.
+narrateur|Elle a visé le but.
+narrateur|Les pieds sont restés dans l'espace montré.
+papa|Tu as passé, puis visé le but ?
+enfant-f|Oui. Dans l'espace montré.
+papa|Bravo. C'est du bon travail.
+narrateur|Le seau fait encore un petit ding.
+narrateur|L'aile jaune n'est plus là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1700,7 +1762,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range les sacs. Flore boit une gorgée.</t>
+          <t>On range les sacs ? Oui, papa. Mila porte un sac. Il est râpeux. Papa porte l'autre sac. Mila boit une gorgée. L'eau est fraîche. L'herbe est encore mouillée. Mes chaussettes aussi. On rentre. Le ballon vient avec nous.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1836,10 +1898,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa range les sacs. Flore boit une gorgée.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>papa|On range les sacs ?
+enfant-f|Oui, papa.
+narrateur|Mila porte un sac.
+narrateur|Il est râpeux.
+narrateur|Papa porte l'autre sac.
+narrateur|Mila boit une gorgée.
+narrateur|L'eau est fraîche.
+papa|L'herbe est encore mouillée.
+enfant-f|Mes chaussettes aussi.
+papa|On rentre. Le ballon vient avec nous.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1864,7 +1934,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le ballon sèche près des sandales. On a visé le but. Oui. Et on a passé le ballon. Dans l'espace montré. Bravo, Mila. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2004,10 +2074,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le ballon sèche près des sandales.
+enfant-f|On a visé le but.
+papa|Oui. Et on a passé le ballon.
+papa|Dans l'espace montré.
+papa|Bravo, Mila.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2138,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.FOOT.001-06.xlsx
+++ b/stories/arbres/ATOM-JEU.FOOT.001-06.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une goutte tombe de la gouttière. Elle fait ding dans le seau gris. Le romarin sent fort, tout près. Les sandales sèchent sur la dalle chaude. Une aile jaune passe au-dessus des pots. Tu as entendu le seau, Mila ? Oui, papa. Ça fait ding. En ce moment, le ballon attend dans l'herbe. L'herbe est encore un peu mouillée. Mila pose la paume sur le ballon. Il est souple, papa. Oui. Il est souple et lisse. Papa pose deux sacs au fond du jardin. C'est le but. Les sacs sont beiges et un peu râpeux. Papa trace un rectangle dans l'herbe. Voici l'espace montré. On reste dans l'espace montré. Dans le rectangle ? Oui. Les pieds restent ici. Mila avance dans l'espace montré. Ses chaussettes vertes sont un peu humides. On va passer le ballon. Puis on vise le but. Mila pousse le ballon vers papa. Le ballon roule, tout mou, dans l'herbe. Bien. Tu as passé le ballon. Papa le rend, tout doucement. Mila le reçoit dans l'espace montré. Maintenant, vise le but. Mila pousse le ballon vers les sacs. Le ballon glisse entre les deux sacs. Il est au fond ! Bravo. Tu as visé le but. Les pieds sont restés dans l'espace montré. Mila ramène le ballon contre son ventre. Une goutte tombe encore dans le seau. On recommence. On passe, puis le but. Mila passe encore le ballon. Papa rend encore le ballon. Mila vise encore le but. Le ballon touche un sac, puis entre. Bravo, Mila. Tu as fait du bon travail. On reste dans l'espace montré. Oui. On passe. On vise le but. Mila essuie une goutte sur le ballon. Le ballon sent l'herbe mouillée. Tu as fini ce tour ? Oui, papa. Bravo. On boit un peu d'eau.</t>
+          <t>Une goutte tombe de la gouttière. Elle fait ding dans le seau gris. Le romarin sent fort, tout près. Les sandales sèchent sur la dalle chaude. Une aile jaune passe au-dessus des pots. Tu as entendu le seau, Mila ? Oui, papa. Ça fait ding. En ce moment, le ballon attend dans l'herbe. L'herbe est encore un peu mouillée. Mila pose la paume sur le ballon. Il est souple, papa. Oui. Il est souple et lisse. Papa pose deux sacs au fond du jardin. C'est le but. Les sacs sont beiges et un peu râpeux. Papa trace un rectangle dans l'herbe. Voici l'espace montré. On reste dans l'espace montré. Dans le rectangle ? Oui. Les pieds restent ici. Mila avance dans l'espace montré. Ses chaussettes vertes sont un peu humides. On va passer le ballon. Puis on vise le but. Mila pousse le ballon vers papa. Le ballon roule, tout mou, dans l'herbe. Bien. Tu as passé le ballon. Papa le rend, tout doucement. Mila le reçoit dans l'espace montré. Maintenant, vise le but. Mila pousse le ballon vers les sacs. Le ballon glisse entre les deux sacs. Il est au fond ! Bravo. Tu as visé le but. Les pieds sont restés dans l'espace montré. Mila ramène le ballon contre son ventre. Une goutte tombe encore dans le seau. On recommence. On passe, puis le but. Mila passe encore le ballon. Papa rend encore le ballon. Mila vise encore le but. Le ballon touche un sac, puis entre. On reste dans l'espace montré. Oui. On passe. On vise le but. Mila essuie une goutte sur le ballon. Le ballon sent l'herbe mouillée. Tu as fini ce tour ? Oui, papa. Bravo. On boit un peu d'eau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Flore et papa sont au jardin. Papa pose deux sacs. C'est le &lt;emphasis level="moderate"&gt;but&lt;/emphasis&gt;. Il trace un rectangle. Papa dit : voici l'espace montré. On reste dans l'espace montré. Flore touche le ballon. Papa dit : on va passer le ballon. Puis on vise le but. Flore passe. Papa rend. Flore pousse le ballon vers le but. Les pieds restent dans l'espace montré.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une goutte tombe de la gouttière. Elle fait ding dans le seau gris. Le romarin sent fort, tout près. Les sandales sèchent sur la dalle chaude. Une aile jaune passe au-dessus des pots. Tu as entendu le seau, Mila ? Oui, papa. Ça fait ding. En ce moment, le ballon attend dans l'herbe. L'herbe est encore un peu mouillée. Mila pose la paume sur le ballon. Il est souple, papa. Oui. Il est souple et lisse. Papa pose deux sacs au fond du jardin. C'est le but. Les sacs sont beiges et un peu râpeux. Papa trace un rectangle dans l'herbe. Voici l'espace montré. On reste dans l'espace montré. Dans le rectangle ? Oui. Les pieds restent ici. Mila avance dans l'espace montré. Ses chaussettes vertes sont un peu humides. On va passer le ballon. Puis on vise le but. Mila pousse le ballon vers papa. Le ballon roule, tout mou, dans l'herbe. Bien. Tu as passé le ballon. Papa le rend, tout doucement. Mila le reçoit dans l'espace montré. Maintenant, vise le but. Mila pousse le ballon vers les sacs. Le ballon glisse entre les deux sacs. Il est au fond ! Bravo. Tu as visé le but. Les pieds sont restés dans l'espace montré. Mila ramène le ballon contre son ventre. Une goutte tombe encore dans le seau. On recommence. On passe, puis le but. Mila passe encore le ballon. Papa rend encore le ballon. Mila vise encore le but. Le ballon touche un sac, puis entre. On reste dans l'espace montré. Oui. On passe. On vise le but. Mila essuie une goutte sur le ballon. Le ballon sent l'herbe mouillée. Tu as fini ce tour ? Oui, papa. Bravo. On boit un peu d'eau.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1366,7 +1366,6 @@
 narrateur|Papa rend encore le ballon.
 narrateur|Mila vise encore le but.
 narrateur|Le ballon touche un sac, puis entre.
-papa|Bravo, Mila. Tu as fait du bon travail.
 enfant-f|On reste dans l'espace montré.
 papa|Oui. On passe. On vise le but.
 narrateur|Mila essuie une goutte sur le ballon.
@@ -1405,7 +1404,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Flore joue au foot. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila joue au foot. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1584,12 +1583,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a passé le ballon. Elle a visé le but. Les pieds sont restés dans l'espace montré. Tu as passé, puis visé le but ? Oui. Dans l'espace montré. Bravo. C'est du bon travail. Le seau fait encore un petit ding. L'aile jaune n'est plus là.</t>
+          <t>Mila a passé le ballon. Elle a visé le but. Les pieds sont restés dans l'espace montré. Tu as passé, puis visé le but ? Oui. Dans l'espace montré. Le seau fait encore un petit ding. L'aile jaune n'est plus là.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Flore a passé le ballon. Elle a visé le &lt;emphasis level="moderate"&gt;but&lt;/emphasis&gt;. Dans l'espace montré.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a passé le ballon. Elle a visé le but. Les pieds sont restés dans l'espace montré. Tu as passé, puis visé le but ? Oui. Dans l'espace montré. Le seau fait encore un petit ding. L'aile jaune n'est plus là.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1733,7 +1732,6 @@
 narrateur|Les pieds sont restés dans l'espace montré.
 papa|Tu as passé, puis visé le but ?
 enfant-f|Oui. Dans l'espace montré.
-papa|Bravo. C'est du bon travail.
 narrateur|Le seau fait encore un petit ding.
 narrateur|L'aile jaune n'est plus là.</t>
         </is>
@@ -1767,7 +1765,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa range les sacs. Flore boit une gorgée.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On range les sacs ? Oui, papa. Mila porte un sac. Il est râpeux. Papa porte l'autre sac. Mila boit une gorgée. L'eau est fraîche. L'herbe est encore mouillée. Mes chaussettes aussi. On rentre. Le ballon vient avec nous.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1934,12 +1932,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le ballon sèche près des sandales. On a visé le but. Oui. Et on a passé le ballon. Dans l'espace montré. Bravo, Mila. L'histoire est finie.</t>
+          <t>Le ballon sèche près des sandales. On a visé le but. Oui. Et on a passé le ballon. Dans l'espace montré. Bravo, Mila.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le ballon sèche près des sandales. On a visé le but. Oui. Et on a passé le ballon. Dans l'espace montré. Bravo, Mila.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2078,8 +2076,7 @@
 enfant-f|On a visé le but.
 papa|Oui. Et on a passé le ballon.
 papa|Dans l'espace montré.
-papa|Bravo, Mila.
-narrateur|L'histoire est finie.</t>
+papa|Bravo, Mila.</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2145,6 +2142,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.FOOT.001-06.xlsx
+++ b/stories/arbres/ATOM-JEU.FOOT.001-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>jardin après la pluie</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Flore, papa</t>
+          <t>Mila, papa</t>
         </is>
       </c>
     </row>
